--- a/메모.xlsx
+++ b/메모.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mbc\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mbc\MBCA\React\React\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A986577-E1F2-4310-AF5C-DAD114F13A7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87EAD6AD-BADF-403B-9F76-5D7050DBA65B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="5" xr2:uid="{8A121186-FB01-46A4-82E5-3C1B4E658CCC}"/>
   </bookViews>
